--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,15 +539,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,102 +643,2318 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786705939</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6.635945</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>228.48997</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.8613</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786704847</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>265.300401</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786704771</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786704503</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786704472</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786704050</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.49999</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.7588</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786700992</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.976923</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>36.69</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786697954</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>49.083612</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>35.77998</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786696250</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>47.70664</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>557.83</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786696222</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1025.894253</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>22.83999</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786695902</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>42.004579</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>296.6897</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786695873</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>643.229702</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>346.54</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786695869</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>641.740741</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786695799</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.851852</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,22 +994,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1026,7 +1034,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1091,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,22 +1218,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1250,7 +1258,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1288,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1298,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,39 +1315,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,31 +1867,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1914,7 +1922,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1944,7 +1952,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,12 +1979,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1986,22 +1994,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2056,7 +2064,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2066,7 +2074,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,12 +2091,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2098,22 +2106,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2138,7 +2146,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2168,7 +2176,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2178,7 +2186,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2195,12 +2203,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2210,22 +2218,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2280,7 +2288,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2307,12 +2315,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2322,12 +2330,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2392,7 +2400,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2402,7 +2410,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2419,27 +2427,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2447,11 +2451,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>346.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786695869</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>641.740741</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2643,12 +2643,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695799</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.851852</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2755,31 +2755,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2802,7 +2810,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2832,7 +2840,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695700</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2842,7 +2850,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>1.33332</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2859,102 +2867,654 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,31 +763,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -810,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,7 +1098,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1218,12 +1210,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1288,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1298,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,31 +1307,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,39 +1755,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1810,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1840,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1850,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,12 +1859,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1882,12 +1874,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1952,7 +1944,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1962,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1979,7 +1971,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1994,12 +1986,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2064,7 +2056,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2074,7 +2066,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2091,7 +2083,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2106,7 +2098,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2176,7 +2168,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2186,7 +2178,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2203,12 +2195,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2218,22 +2210,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2288,7 +2280,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2298,7 +2290,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2315,12 +2307,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2330,22 +2322,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2370,7 +2362,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2400,7 +2392,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2410,7 +2402,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2427,7 +2419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2435,23 +2427,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2546,22 +2546,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2643,12 +2643,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2770,22 +2770,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2867,27 +2867,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2895,11 +2891,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2952,7 +2944,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2962,7 +2954,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2979,12 +2971,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2994,7 +2986,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>346.54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3064,7 +3056,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786695869</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3074,7 +3066,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>641.740741</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3091,12 +3083,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3106,7 +3098,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3176,7 +3168,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786695799</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3186,7 +3178,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.851852</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3203,12 +3195,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3218,22 +3210,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3258,7 +3250,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3288,7 +3280,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695700</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3298,7 +3290,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.33332</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3315,23 +3307,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>484.79999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3339,7 +3335,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695653</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>897.777759</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3419,102 +3419,542 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,31 +643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,23 +747,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,39 +851,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -899,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -979,31 +963,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1011,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,31 +1067,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1123,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,39 +1163,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1235,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1322,22 +1282,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1434,22 +1394,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1459,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1504,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,39 +1491,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1571,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1616,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1651,31 +1603,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1683,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1728,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,31 +1699,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1787,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1832,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1867,31 +1819,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1899,27 +1843,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1944,17 +1888,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,7 +1915,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1986,22 +1930,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2011,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2056,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2091,31 +2035,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2123,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2168,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2195,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2203,31 +2139,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2235,27 +2163,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2280,17 +2208,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2307,39 +2235,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2347,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2392,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2419,7 +2339,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2427,31 +2347,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2459,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2504,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2531,39 +2443,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2571,27 +2475,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2616,17 +2520,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2643,12 +2547,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,22 +2562,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2683,27 +2587,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2728,17 +2632,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2755,12 +2659,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2770,22 +2674,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2795,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2840,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2867,31 +2771,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2899,27 +2811,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2944,17 +2856,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2971,12 +2883,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2986,22 +2898,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3011,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3056,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3083,12 +2995,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3098,22 +3010,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3123,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3168,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3195,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3203,31 +3115,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3235,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3280,17 +3184,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3307,39 +3211,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3347,27 +3243,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3392,17 +3288,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3419,39 +3315,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3459,27 +3347,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3504,17 +3392,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3531,12 +3419,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3546,22 +3434,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3571,27 +3459,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3616,17 +3504,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3643,12 +3531,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3658,22 +3546,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3683,27 +3571,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3728,17 +3616,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3755,7 +3643,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3763,15 +3651,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3779,7 +3671,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3832,7 +3728,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3842,7 +3738,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3859,102 +3755,3318 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>66.68</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786714580</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>134.707071</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.625</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786714022</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>49.088</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6.89</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.4937</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786713936</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>13.95443</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.76999</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LASK Linz -0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786712107</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2.681803</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2515.19</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786711888</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>4625.636782</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.5413</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786710267</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>48.258661</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786709725</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>41.011494</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.6612</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>LASK Linz -0.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786709683</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3.493384</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>91.41</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786706976</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>168.110345</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786705939</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6.635945</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>228.48997</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.8613</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786704847</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>265.300401</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786704771</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786704503</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786704472</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786704050</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.49999</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.7588</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786700992</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1.976923</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>36.69</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786697954</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>49.083612</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>35.77998</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786696250</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>47.70664</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>557.83</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786696222</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1025.894253</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22.83999</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786695902</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>42.004579</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>296.6897</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786695873</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>643.229702</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>346.54</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786695869</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>641.740741</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786695799</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1.851852</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,15 +643,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,19 +755,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -767,11 +771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +862,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,23 +963,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1067,23 +1075,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1106,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,31 +1179,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1210,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1282,22 +1306,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1322,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1387,19 +1411,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1407,11 +1427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1434,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1502,12 +1518,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1538,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,15 +1619,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1619,7 +1639,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1627,27 +1651,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1696,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1707,31 +1731,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1754,7 +1770,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1784,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1822,17 +1838,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1874,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1923,19 +1939,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1943,26 +1955,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -2000,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,28 +2035,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2074,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2104,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2114,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2139,23 +2147,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2178,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2208,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2218,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2243,23 +2259,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2282,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2312,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,17 +2374,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2386,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2416,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,23 +2467,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2490,7 +2514,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2520,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,12 +2571,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2562,47 +2586,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2632,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2642,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,62 +2683,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,12 +2787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2786,12 +2802,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2801,7 +2817,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2811,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2856,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,39 +2899,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2938,7 +2946,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2968,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,27 +3003,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3023,11 +3027,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Wolfsberger AC</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3035,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3118,17 +3118,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3211,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3222,17 +3222,17 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,23 +3315,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,12 +3419,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3546,22 +3546,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau +1</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3571,27 +3571,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3658,22 +3658,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3683,27 +3683,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3795,27 +3795,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3840,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,31 +3867,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3899,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3944,17 +3952,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,39 +3979,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,7 +4083,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4091,31 +4091,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4123,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4168,17 +4160,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,7 +4187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4203,31 +4195,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4235,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4280,17 +4264,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,7 +4291,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4322,22 +4306,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4347,27 +4331,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4376,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,7 +4403,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4434,22 +4418,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4459,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4504,17 +4488,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,12 +4515,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4546,22 +4530,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4586,7 +4570,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4616,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4626,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,12 +4627,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4658,22 +4642,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4698,7 +4682,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4712,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4722,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,7 +4739,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4763,31 +4747,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4810,7 +4786,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4875,23 +4851,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4914,7 +4898,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4944,7 +4928,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4954,7 +4938,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4971,7 +4955,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4986,22 +4970,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5026,7 +5010,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5056,7 +5040,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5066,7 +5050,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,7 +5067,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5098,22 +5082,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5138,7 +5122,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5168,7 +5152,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5178,7 +5162,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5195,7 +5179,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5210,22 +5194,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5250,7 +5234,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5280,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5290,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5307,7 +5291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5322,22 +5306,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5362,7 +5346,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5392,7 +5376,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5402,7 +5386,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5419,12 +5403,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5434,22 +5418,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5474,7 +5458,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5504,7 +5488,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5514,7 +5498,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5531,12 +5515,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5546,22 +5530,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5586,7 +5570,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5616,7 +5600,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5626,7 +5610,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5643,7 +5627,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5658,22 +5642,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5698,7 +5682,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5728,7 +5712,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5738,7 +5722,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5755,39 +5739,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5810,7 +5786,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5840,7 +5816,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5850,7 +5826,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5867,12 +5843,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5882,22 +5858,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5922,7 +5898,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5952,7 +5928,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5962,7 +5938,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5979,7 +5955,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5987,23 +5963,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6026,7 +6010,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6056,7 +6040,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6066,7 +6050,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6083,12 +6067,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6098,22 +6082,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6138,7 +6122,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6168,7 +6152,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6178,7 +6162,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6195,12 +6179,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6210,22 +6194,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6250,7 +6234,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6280,7 +6264,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6290,7 +6274,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6307,12 +6291,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6322,12 +6306,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6376,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6402,7 +6386,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6419,12 +6403,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6434,22 +6418,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6474,7 +6458,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6504,7 +6488,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6514,7 +6498,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6531,12 +6515,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6546,22 +6530,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6586,7 +6570,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6616,7 +6600,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6626,7 +6610,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6643,12 +6627,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6658,12 +6642,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6728,7 +6712,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6738,7 +6722,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6755,12 +6739,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6770,12 +6754,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6840,7 +6824,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6850,7 +6834,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6867,23 +6851,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6944,7 +6928,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6954,7 +6938,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6971,102 +6955,990 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>346.54</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786695869</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>641.740741</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786695799</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1.851852</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
+          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.33999</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786795497</t>
+          <t>1786858705</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.425321</t>
+          <t>57.91411</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
+          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786793761</t>
+          <t>1786858045</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>195.84</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
+          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,15 +755,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786857999</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>29.662651</t>
+          <t>71.84466</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
+          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +870,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.68844</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>24.608431</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
+          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,31 +971,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.61999</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -995,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786792979</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12.259241</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
+          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1107,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786792948</t>
+          <t>1786855348</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>12.240741</t>
+          <t>80.645161</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,31 +1179,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1234,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786792921</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>24.587678</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1306,22 +1290,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.80999</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1346,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786792918</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>24.57552</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1414,12 +1398,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1480,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1518,17 +1502,17 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1554,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1651,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1696,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1707,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1731,23 +1715,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1770,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1800,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,7 +1819,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1835,23 +1827,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1939,23 +1939,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1978,7 +1986,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,23 +2043,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2147,31 +2155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2291,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2374,12 +2374,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,7 +2467,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2478,12 +2478,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2579,31 +2579,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2626,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2656,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2675,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2730,7 +2722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,7 +2779,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2802,39 +2794,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -2842,7 +2834,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2907,23 +2899,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3014,12 +3014,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3118,17 +3118,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3211,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3219,15 +3219,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3235,7 +3239,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3288,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,28 +3323,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3362,7 +3370,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3392,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,12 +3427,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3434,12 +3442,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3449,32 +3457,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3504,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,62 +3539,54 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,27 +3643,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3671,11 +3667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3683,27 +3675,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3728,17 +3720,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,39 +3747,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3810,7 +3794,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3840,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,39 +3851,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Wolfsberger AC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3907,27 +3883,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3928,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,23 +3955,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4056,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,31 +4059,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4130,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4160,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,23 +4171,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4211,7 +4199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4264,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4274,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,12 +4283,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4306,52 +4298,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4376,17 +4368,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,12 +4395,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4418,22 +4410,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau +1</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4443,27 +4435,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,17 +4480,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,7 +4507,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4530,22 +4522,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4555,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4600,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4635,31 +4627,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4667,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4712,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4739,7 +4723,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4750,17 +4734,17 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4771,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,39 +4827,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4883,27 +4859,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4928,17 +4904,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4955,7 +4931,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4970,22 +4946,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4995,27 +4971,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5040,17 +5016,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,7 +5043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5082,22 +5058,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5107,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5152,17 +5128,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,12 +5155,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5194,12 +5170,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5264,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,7 +5267,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5306,22 +5282,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5346,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5376,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5386,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,7 +5379,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5411,31 +5387,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5458,7 +5426,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5488,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5498,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,7 +5483,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5530,22 +5498,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5570,7 +5538,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5600,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5610,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5627,7 +5595,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5642,22 +5610,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5682,7 +5650,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5712,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5722,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5739,31 +5707,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5786,7 +5762,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5816,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5826,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5843,7 +5819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5858,22 +5834,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5898,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5928,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5938,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5955,7 +5931,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5970,22 +5946,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6010,7 +5986,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6040,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6050,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6067,7 +6043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6082,22 +6058,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6122,7 +6098,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6152,7 +6128,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6162,7 +6138,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6179,12 +6155,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6194,22 +6170,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6234,7 +6210,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6264,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6274,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6291,12 +6267,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6306,22 +6282,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6346,7 +6322,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6376,7 +6352,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6386,7 +6362,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6403,39 +6379,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6458,7 +6426,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6488,7 +6456,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6498,7 +6466,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6515,7 +6483,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6530,7 +6498,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6600,7 +6568,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6610,7 +6578,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6627,12 +6595,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6642,22 +6610,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6682,7 +6650,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6712,7 +6680,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6722,7 +6690,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6739,12 +6707,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6754,22 +6722,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6794,7 +6762,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6824,7 +6792,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6834,7 +6802,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6851,7 +6819,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6859,23 +6827,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6898,7 +6874,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6928,7 +6904,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6938,7 +6914,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6955,12 +6931,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6970,22 +6946,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7010,7 +6986,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7040,7 +7016,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7050,7 +7026,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7067,12 +7043,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7082,22 +7058,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7122,7 +7098,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7152,7 +7128,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7162,7 +7138,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7179,7 +7155,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7194,7 +7170,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7264,7 +7240,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7274,7 +7250,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7291,12 +7267,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7306,12 +7282,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7376,7 +7352,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7386,7 +7362,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7403,12 +7379,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7418,12 +7394,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7488,7 +7464,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7498,7 +7474,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7515,27 +7491,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7543,11 +7515,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7600,7 +7568,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7610,7 +7578,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7627,12 +7595,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7642,7 +7610,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>346.54</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7712,7 +7680,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695869</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7722,7 +7690,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>641.740741</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7739,23 +7707,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7763,7 +7735,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7816,7 +7792,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695799</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7826,7 +7802,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>1.851852</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7843,102 +7819,766 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
+          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,7 +542,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>17.09998</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786858705</t>
+          <t>1786863582</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>57.91411</t>
+          <t>20.981571</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,54 +635,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
+          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786858045</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>195.84</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,54 +739,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
+          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -802,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786857999</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>71.84466</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
+          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>53.92996</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786863030</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>66.17173</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
+          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,17 +958,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -995,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786858705</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>57.91411</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,23 +1051,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
+          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1091,7 +1079,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1099,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786855348</t>
+          <t>1786858045</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>80.645161</t>
+          <t>195.84</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
+          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,23 +1171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.33999</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1203,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786795497</t>
+          <t>1786857999</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.425321</t>
+          <t>71.84466</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
+          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1283,31 +1283,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1315,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786793761</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
+          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1398,17 +1390,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1419,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.662651</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,28 +1483,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
+          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.68844</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786855348</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>24.608431</t>
+          <t>80.645161</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,31 +1595,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.61999</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1650,7 +1634,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1664,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786792979</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1674,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>12.259241</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1722,22 +1706,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1762,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786792948</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>12.240741</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1827,31 +1811,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1874,7 +1850,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786792921</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>24.587678</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1939,31 +1915,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.80999</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1986,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2016,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786792918</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>24.57552</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2011,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2051,23 +2019,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2090,7 +2066,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2120,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,23 +2131,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2194,7 +2178,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2266,22 +2250,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2291,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2347,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2371,23 +2355,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2410,7 +2402,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2442,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2478,7 +2470,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2544,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2582,7 +2574,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2648,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2658,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,23 +2667,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2699,7 +2695,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2787,31 +2787,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2834,7 +2826,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2864,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2883,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,19 +2891,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2919,11 +2907,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2946,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3014,12 +2998,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3050,7 +3034,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,23 +3091,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3154,7 +3138,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3226,12 +3210,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3296,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,7 +3307,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3331,23 +3315,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3370,7 +3362,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3400,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3410,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3419,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3435,19 +3427,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3455,26 +3443,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -3482,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3512,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3550,17 +3534,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3586,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3651,23 +3635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3690,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3720,7 +3712,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3730,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3758,12 +3750,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3824,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3859,23 +3851,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,28 +3955,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,27 +4059,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4087,34 +4083,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4144,7 +4136,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4146,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,62 +4163,54 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4256,7 +4240,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4250,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,39 +4267,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4323,27 +4299,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4368,17 +4344,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,39 +4371,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4450,7 +4418,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4480,7 +4448,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4458,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,12 +4475,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4522,12 +4490,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4537,7 +4505,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4547,27 +4515,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4592,17 +4560,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,23 +4587,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4643,7 +4615,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4666,7 +4642,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4672,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4682,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,31 +4699,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4755,27 +4739,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,17 +4784,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,31 +4811,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4874,7 +4866,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4904,7 +4896,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4914,7 +4906,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4931,12 +4923,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4946,52 +4938,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5016,17 +5008,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,7 +5035,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5051,31 +5043,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau +1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5083,27 +5067,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,17 +5112,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,39 +5139,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5195,27 +5171,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5240,17 +5216,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,7 +5243,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5275,31 +5251,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5307,27 +5275,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5352,17 +5320,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,7 +5347,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5387,23 +5355,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5411,27 +5387,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,17 +5432,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,12 +5459,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5498,22 +5474,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5523,27 +5499,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5568,17 +5544,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,12 +5571,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5610,22 +5586,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5650,7 +5626,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5656,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5666,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,7 +5683,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5722,22 +5698,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5762,7 +5738,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5792,7 +5768,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5778,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,7 +5795,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5827,31 +5803,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5874,7 +5842,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5904,7 +5872,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5882,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,12 +5899,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5946,22 +5914,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5986,7 +5954,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6016,7 +5984,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +5994,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6058,12 +6026,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6128,7 +6096,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6138,7 +6106,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,12 +6123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6170,7 +6138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6240,7 +6208,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6218,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,7 +6235,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6282,12 +6250,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6352,7 +6320,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6362,7 +6330,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,31 +6347,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6426,7 +6402,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6456,7 +6432,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6466,7 +6442,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6483,7 +6459,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6498,22 +6474,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6538,7 +6514,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6568,7 +6544,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6578,7 +6554,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6595,12 +6571,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6610,22 +6586,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6650,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6680,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6690,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6707,7 +6683,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6722,22 +6698,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6762,7 +6738,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6792,7 +6768,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6802,7 +6778,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6819,39 +6795,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6874,7 +6842,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6904,7 +6872,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6914,7 +6882,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,12 +6899,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6946,12 +6914,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7016,7 +6984,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7026,7 +6994,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7043,7 +7011,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7058,12 +7026,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7128,7 +7096,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7138,7 +7106,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7155,7 +7123,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7170,7 +7138,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7240,7 +7208,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7250,7 +7218,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7267,12 +7235,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7282,22 +7250,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7322,7 +7290,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7352,7 +7320,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7362,7 +7330,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7379,12 +7347,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7394,22 +7362,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7434,7 +7402,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7464,7 +7432,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7474,7 +7442,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7491,7 +7459,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7499,23 +7467,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7538,7 +7514,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7568,7 +7544,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7578,7 +7554,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7595,12 +7571,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7610,22 +7586,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7650,7 +7626,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7680,7 +7656,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7690,7 +7666,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,12 +7683,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7722,12 +7698,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7792,7 +7768,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7802,7 +7778,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7819,12 +7795,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7834,22 +7810,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7874,7 +7850,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7904,7 +7880,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7914,7 +7890,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7931,27 +7907,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7959,11 +7931,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8016,7 +7984,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8026,7 +7994,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8043,12 +8011,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8058,7 +8026,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>346.54</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8128,7 +8096,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786695869</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8138,7 +8106,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>641.740741</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8155,12 +8123,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8170,7 +8138,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8240,7 +8208,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786695799</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8250,7 +8218,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.851852</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8267,12 +8235,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8282,22 +8250,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8322,7 +8290,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8352,7 +8320,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695700</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8362,7 +8330,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.33332</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,23 +8347,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>484.79999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8403,7 +8375,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8456,7 +8432,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695653</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8466,7 +8442,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>897.777759</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8483,102 +8459,542 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
+          <t>0xda8cf2ddfe903270bba7449c2f7bf9acbc33b05eac7a7431fb09e9ee64853f08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.09998</t>
+          <t>229.82999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786863582</t>
+          <t>1786882671</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20.981571</t>
+          <t>370.693532</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
+          <t>0x81f5b415be2d9f364b502493091c0350e0da5326ca647b3480b14b2bb1c334fb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1.00422</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786878747</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>2.391</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
+          <t>0xf3bc0100004de3bde89c6fd3055ba5bd9878df9155f316db14ec34daf9886062</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>56.56997</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786877644</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>68.15659</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
+          <t>0xef05d2408f42aecc4b2a6cf4b72c3ef0cd01f9213fe2a25ca0dfa829110934ff</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,12 +854,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.92996</t>
+          <t>57.83997</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786863030</t>
+          <t>1786877501</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>66.17173</t>
+          <t>69.686711</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
+          <t>0x9ff5d2cde067c6ad242419d3d9bdbaf418ce158b1f50ec823b76bb08b5b0f34f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786858705</t>
+          <t>1786876123</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>57.91411</t>
+          <t>2.793017</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,54 +1051,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
+          <t>0x45639b4a3510d9a1f0dc1a3c57bd5c2c43f6011c9a4874e4291a0f1361f866fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>591.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -1106,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786858045</t>
+          <t>1786876048</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>195.84</t>
+          <t>1179.850374</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
+          <t>0xfe72d608227d2615a1b90aefefca2cbbb3e0ff5a0061bb2df632410a9f0f9530</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1171,19 +1163,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1191,11 +1179,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1203,27 +1187,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1232,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786857999</t>
+          <t>1786872056</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>71.84466</t>
+          <t>54.715152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,28 +1259,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
+          <t>0xb84c412ef91494a7066f12271852db25d63c75af7c1e9b26e57ed1c4991acec5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.4238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1307,27 +1291,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1336,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786870513</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>94.348083</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,18 +1363,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
+          <t>0x2f524160a862509b29112385fcf72a4688928c84e4aaf6160e6762e112dafd6d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>900.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1456,7 +1440,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786870469</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1450,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>1796.508728</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,23 +1467,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
+          <t>0x43b6ea29196f2fdd23ccb2434b2a5c2303cbddc27e7b9ab1393a2c1d934e15db</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1515,27 +1499,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1544,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786855348</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>80.645161</t>
+          <t>310.214286</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1571,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
+          <t>0x3e487ada34f8a35d4e11d554823d4747f6bacd7acbc906a4760553dcccc48e20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1595,23 +1579,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.33999</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1619,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xe871719b5fd77c56cc970200624c2bdc63c0892cbbb3c746da8dd2228878d10d</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786795497</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.425321</t>
+          <t>153.55102</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
+          <t>0x5fdca699fdb043ee4eed8313b2eba1678a243ef8458326568b7e2b202efe6fb1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1706,12 +1698,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1721,7 +1713,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1731,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786793761</t>
+          <t>1786869580</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>6.179104</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
+          <t>0x7e0b4b4cd37a32b012ae08e8fafc2a2c8bc292701e823cf78c0980f92bc7a1c0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1814,12 +1806,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>2.08996</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.895</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1835,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1880,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786868988</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>29.662651</t>
+          <t>2.335151</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,7 +1899,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
+          <t>0x21823d634d9b05dcf49935cd5a225282d8f45e2f2bbb6cbd1e8fdfeb74e09dae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,17 +1910,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13.68844</t>
+          <t>6.64999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1939,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786868846</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>24.608431</t>
+          <t>10.72579</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +2003,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
+          <t>0x765333b5d50950a47c39ac8b8b82009e8a312c78991c1a5c77c6c4f06f399d84</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2026,22 +2018,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.61999</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2051,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786792979</t>
+          <t>1786867972</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>12.259241</t>
+          <t>33.044776</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,7 +2115,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
+          <t>0x05d81bcc4dc3a80e0a909b3e7fca461f800353de941a393c27bdd25ac4a5fd4d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2138,22 +2130,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2163,27 +2155,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2200,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786792948</t>
+          <t>1786867801</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>12.240741</t>
+          <t>23.701493</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2227,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
+          <t>0x74c478c25c884e128702e32231056f1f8df3fecc5378ed83072476df5090e33f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2243,31 +2235,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>12.65998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2275,27 +2259,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2320,17 +2304,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786792921</t>
+          <t>1786866135</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>24.587678</t>
+          <t>15.462571</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,39 +2331,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
+          <t>0xd92875c7cde785279801c4010a511eb03a3411ac6a04b8a5c60708f8bfdfde3a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.80999</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2387,27 +2363,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2408,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786792918</t>
+          <t>1786865292</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>24.57552</t>
+          <t>5.028571</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,23 +2435,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0xb3ba12049a809b51522b33ed465df69f8887adf26be7e2a64fe1d112796b79e1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.1875</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2483,7 +2463,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2491,27 +2475,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2520,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786864292</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2547,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0x797638d4b1a279644b7c09a6f87d4f0bc84ed28a77802f60772f9cb336839a69</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2574,17 +2558,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2595,27 +2579,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2624,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,7 +2651,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0x1de2155e1c3ba327729349e4b0db5dcab8d6a26fc4885bf5cb6fc10388a34aac</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2675,31 +2659,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2707,27 +2683,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2728,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2755,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2790,12 +2766,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>17.09998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2811,27 +2787,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2856,17 +2832,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786863582</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>20.981571</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,28 +2859,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2915,27 +2891,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2960,17 +2936,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,28 +2963,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3019,27 +2995,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3064,17 +3040,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,23 +3067,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>53.92996</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3123,27 +3099,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3168,17 +3144,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786863030</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>66.17173</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,7 +3171,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3203,31 +3179,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3235,27 +3203,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3280,17 +3248,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786858705</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>57.91411</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,7 +3275,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3322,12 +3290,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3337,7 +3305,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3347,27 +3315,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3392,17 +3360,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786858045</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>195.84</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,7 +3387,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3427,15 +3395,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3443,7 +3415,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3451,27 +3427,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3496,17 +3472,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786857999</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>71.84466</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,7 +3499,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3534,17 +3510,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3555,27 +3531,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3600,17 +3576,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3603,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3635,31 +3611,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3667,27 +3635,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3712,17 +3680,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,28 +3707,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3771,27 +3739,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3816,17 +3784,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786855348</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>80.645161</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,7 +3811,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3851,46 +3819,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -3898,7 +3858,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3888,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3898,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,7 +3915,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3963,23 +3923,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4002,7 +3970,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4000,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4010,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,7 +4027,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4070,12 +4038,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4136,7 +4104,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4146,7 +4114,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,7 +4131,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4174,12 +4142,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4240,7 +4208,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4250,7 +4218,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4267,7 +4235,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4275,23 +4243,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4314,7 +4290,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4344,7 +4320,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4354,7 +4330,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4371,31 +4347,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4418,7 +4402,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4448,7 +4432,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4458,7 +4442,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4475,12 +4459,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4490,47 +4474,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4560,7 +4544,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4570,7 +4554,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4587,12 +4571,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4602,47 +4586,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4682,7 +4666,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,27 +4683,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4727,11 +4707,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4739,27 +4715,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4784,17 +4760,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4811,39 +4787,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4866,7 +4834,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4896,7 +4864,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4906,7 +4874,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4923,12 +4891,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4938,12 +4906,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4953,32 +4921,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>Wolfsberger AC</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Wolfsberger AC</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5008,7 +4976,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5018,7 +4986,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5035,7 +5003,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5046,12 +5014,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5112,7 +5080,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5122,7 +5090,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5139,7 +5107,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5150,17 +5118,17 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5186,7 +5154,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5216,7 +5184,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5226,7 +5194,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5243,7 +5211,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5254,12 +5222,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5290,7 +5258,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5320,7 +5288,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5330,7 +5298,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5347,54 +5315,46 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -5402,7 +5362,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5432,7 +5392,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5442,7 +5402,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5459,7 +5419,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5474,22 +5434,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau +1</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5499,27 +5459,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5544,17 +5504,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5571,12 +5531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5586,22 +5546,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5611,27 +5571,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5656,17 +5616,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5683,7 +5643,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5691,31 +5651,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5723,27 +5675,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5768,17 +5720,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5795,7 +5747,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5806,17 +5758,17 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5827,27 +5779,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5872,17 +5824,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5899,12 +5851,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5914,22 +5866,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5939,27 +5891,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5984,17 +5936,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6011,7 +5963,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6019,31 +5971,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6051,27 +5995,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6096,17 +6040,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,7 +6067,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6138,22 +6082,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6163,27 +6107,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6208,17 +6152,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6235,7 +6179,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6243,19 +6187,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6263,11 +6203,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6275,27 +6211,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6320,17 +6256,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6347,7 +6283,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6355,31 +6291,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6387,27 +6315,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6432,17 +6360,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6459,7 +6387,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6467,31 +6395,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6499,27 +6419,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6544,17 +6464,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,39 +6491,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6611,27 +6523,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6656,17 +6568,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6683,39 +6595,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6723,27 +6627,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6768,17 +6672,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6795,23 +6699,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6819,7 +6727,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6827,27 +6739,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6872,17 +6784,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6899,12 +6811,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6914,22 +6826,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6939,27 +6851,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6984,17 +6896,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7011,12 +6923,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7026,22 +6938,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7051,27 +6963,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7096,17 +7008,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7123,12 +7035,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7138,22 +7050,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7163,27 +7075,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7208,17 +7120,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7235,12 +7147,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7250,22 +7162,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7275,27 +7187,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7320,17 +7232,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,39 +7259,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7387,27 +7291,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7432,17 +7336,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7459,7 +7363,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7467,19 +7371,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7487,11 +7387,7 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7499,27 +7395,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7544,17 +7440,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7571,7 +7467,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7579,31 +7475,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7611,27 +7499,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7656,17 +7544,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7683,12 +7571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7698,22 +7586,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7723,27 +7611,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7768,17 +7656,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7795,12 +7683,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7810,22 +7698,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7835,27 +7723,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7880,17 +7768,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7907,23 +7795,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7931,7 +7823,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7984,7 +7880,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7994,7 +7890,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8011,12 +7907,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8026,22 +7922,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8066,7 +7962,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8096,7 +7992,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8106,7 +8002,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8123,39 +8019,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8178,7 +8066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8208,7 +8096,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8218,7 +8106,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8235,12 +8123,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8250,22 +8138,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8290,7 +8178,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8320,7 +8208,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8330,7 +8218,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8347,12 +8235,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8362,22 +8250,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8402,7 +8290,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8432,7 +8320,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8442,7 +8330,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8459,12 +8347,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8474,12 +8362,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8544,7 +8432,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8554,7 +8442,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8571,12 +8459,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8586,12 +8474,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8656,7 +8544,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8666,7 +8554,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8683,12 +8571,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8698,12 +8586,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8768,7 +8656,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8778,7 +8666,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8795,31 +8683,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>LASK Linz -0.5</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8842,7 +8738,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8872,7 +8768,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8882,7 +8778,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8899,102 +8795,2430 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>91.41</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786706976</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>168.110345</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786705939</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>6.635945</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>228.48997</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.8613</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786704847</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>265.300401</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786704771</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786704503</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786704472</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786704050</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.49999</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.7588</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786700992</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1.976923</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>36.69</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786697954</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>49.083612</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>35.77998</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786696250</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>47.70664</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>557.83</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786696222</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1025.894253</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>22.83999</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786695902</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>42.004579</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>296.6897</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786695873</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>643.229702</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>346.54</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786695869</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>641.740741</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786695799</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1.851852</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xda8cf2ddfe903270bba7449c2f7bf9acbc33b05eac7a7431fb09e9ee64853f08</t>
+          <t>0x812fa3d4e263ebdb16994a6b2737919b3df2a23ada0e5a867604cbca04e1ea98</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>229.82999</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786882671</t>
+          <t>1786888022</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>370.693532</t>
+          <t>4.192872</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x81f5b415be2d9f364b502493091c0350e0da5326ca647b3480b14b2bb1c334fb</t>
+          <t>0x00cc1ede6077ec76316a51d8963b5407eb467c5c0c211b5752bec8b449981c8f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.00422</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786878747</t>
+          <t>1786887670</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>7.186441</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf3bc0100004de3bde89c6fd3055ba5bd9878df9155f316db14ec34daf9886062</t>
+          <t>0xe704a4356af06d75246cd4617d655ea10fbf4620e809fa4e2d8dbcf524f89ae7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,17 +766,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.56997</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786877644</t>
+          <t>1786887365</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>68.15659</t>
+          <t>20.901961</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +859,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xef05d2408f42aecc4b2a6cf4b72c3ef0cd01f9213fe2a25ca0dfa829110934ff</t>
+          <t>0x3042c7a60b1ec4ef2d88e5ecc7a771ba0a2dd47f415b018e857ba99cab944459</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.83997</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -867,7 +887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -875,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786877501</t>
+          <t>1786886556</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>69.686711</t>
+          <t>58.169492</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9ff5d2cde067c6ad242419d3d9bdbaf418ce158b1f50ec823b76bb08b5b0f34f</t>
+          <t>0xda8cf2ddfe903270bba7449c2f7bf9acbc33b05eac7a7431fb09e9ee64853f08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>229.82999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786876123</t>
+          <t>1786882671</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.793017</t>
+          <t>370.693532</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x45639b4a3510d9a1f0dc1a3c57bd5c2c43f6011c9a4874e4291a0f1361f866fc</t>
+          <t>0x81f5b415be2d9f364b502493091c0350e0da5326ca647b3480b14b2bb1c334fb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>591.4</t>
+          <t>1.00422</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786876048</t>
+          <t>1786878747</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1179.850374</t>
+          <t>2.391</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xfe72d608227d2615a1b90aefefca2cbbb3e0ff5a0061bb2df632410a9f0f9530</t>
+          <t>0xf3bc0100004de3bde89c6fd3055ba5bd9878df9155f316db14ec34daf9886062</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,12 +1190,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>56.56997</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786872056</t>
+          <t>1786877644</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>54.715152</t>
+          <t>68.15659</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,23 +1283,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb84c412ef91494a7066f12271852db25d63c75af7c1e9b26e57ed1c4991acec5</t>
+          <t>0xef05d2408f42aecc4b2a6cf4b72c3ef0cd01f9213fe2a25ca0dfa829110934ff</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>57.83997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4238</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1306,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1336,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786870513</t>
+          <t>1786877501</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>94.348083</t>
+          <t>69.686711</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2f524160a862509b29112385fcf72a4688928c84e4aaf6160e6762e112dafd6d</t>
+          <t>0x9ff5d2cde067c6ad242419d3d9bdbaf418ce158b1f50ec823b76bb08b5b0f34f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1374,7 +1398,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>900.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1440,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786870469</t>
+          <t>1786876123</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1450,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1796.508728</t>
+          <t>2.793017</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,28 +1491,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x43b6ea29196f2fdd23ccb2434b2a5c2303cbddc27e7b9ab1393a2c1d934e15db</t>
+          <t>0x45639b4a3510d9a1f0dc1a3c57bd5c2c43f6011c9a4874e4291a0f1361f866fc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>130.29</t>
+          <t>591.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1499,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1544,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786870403</t>
+          <t>1786876048</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>310.214286</t>
+          <t>1179.850374</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1571,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x3e487ada34f8a35d4e11d554823d4747f6bacd7acbc906a4760553dcccc48e20</t>
+          <t>0xfe72d608227d2615a1b90aefefca2cbbb3e0ff5a0061bb2df632410a9f0f9530</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1579,19 +1603,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1599,11 +1619,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1626,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe871719b5fd77c56cc970200624c2bdc63c0892cbbb3c746da8dd2228878d10d</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1656,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786870403</t>
+          <t>1786872056</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1666,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>153.55102</t>
+          <t>54.715152</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,27 +1699,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5fdca699fdb043ee4eed8313b2eba1678a243ef8458326568b7e2b202efe6fb1</t>
+          <t>0xb84c412ef91494a7066f12271852db25d63c75af7c1e9b26e57ed1c4991acec5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.4238</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1711,11 +1723,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TSV Hartberg</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -1723,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1768,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786869580</t>
+          <t>1786870513</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6.179104</t>
+          <t>94.348083</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,28 +1803,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7e0b4b4cd37a32b012ae08e8fafc2a2c8bc292701e823cf78c0980f92bc7a1c0</t>
+          <t>0x2f524160a862509b29112385fcf72a4688928c84e4aaf6160e6762e112dafd6d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.08996</t>
+          <t>900.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1842,7 +1850,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786868988</t>
+          <t>1786870469</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.335151</t>
+          <t>1796.508728</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x21823d634d9b05dcf49935cd5a225282d8f45e2f2bbb6cbd1e8fdfeb74e09dae</t>
+          <t>0x43b6ea29196f2fdd23ccb2434b2a5c2303cbddc27e7b9ab1393a2c1d934e15db</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,12 +1918,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.64999</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1931,27 +1939,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1976,17 +1984,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786868846</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>10.72579</t>
+          <t>310.214286</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,7 +2011,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x765333b5d50950a47c39ac8b8b82009e8a312c78991c1a5c77c6c4f06f399d84</t>
+          <t>0x3e487ada34f8a35d4e11d554823d4747f6bacd7acbc906a4760553dcccc48e20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2018,12 +2026,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2033,7 +2041,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2043,27 +2051,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
+          <t>0xe871719b5fd77c56cc970200624c2bdc63c0892cbbb3c746da8dd2228878d10d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2096,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786867972</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>33.044776</t>
+          <t>153.55102</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x05d81bcc4dc3a80e0a909b3e7fca461f800353de941a393c27bdd25ac4a5fd4d</t>
+          <t>0x5fdca699fdb043ee4eed8313b2eba1678a243ef8458326568b7e2b202efe6fb1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786867801</t>
+          <t>1786869580</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>23.701493</t>
+          <t>6.179104</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x74c478c25c884e128702e32231056f1f8df3fecc5378ed83072476df5090e33f</t>
+          <t>0x7e0b4b4cd37a32b012ae08e8fafc2a2c8bc292701e823cf78c0980f92bc7a1c0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2238,12 +2246,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.65998</t>
+          <t>2.08996</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.895</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2259,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2304,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786866135</t>
+          <t>1786868988</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15.462571</t>
+          <t>2.335151</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,23 +2339,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd92875c7cde785279801c4010a511eb03a3411ac6a04b8a5c60708f8bfdfde3a</t>
+          <t>0x21823d634d9b05dcf49935cd5a225282d8f45e2f2bbb6cbd1e8fdfeb74e09dae</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>6.64999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4375</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2363,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2408,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786865292</t>
+          <t>1786868846</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5.028571</t>
+          <t>10.72579</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,12 +2443,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb3ba12049a809b51522b33ed465df69f8887adf26be7e2a64fe1d112796b79e1</t>
+          <t>0x765333b5d50950a47c39ac8b8b82009e8a312c78991c1a5c77c6c4f06f399d84</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2450,12 +2458,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1875</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2465,7 +2473,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2475,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786864292</t>
+          <t>1786867972</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>33.044776</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,7 +2555,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x797638d4b1a279644b7c09a6f87d4f0bc84ed28a77802f60772f9cb336839a69</t>
+          <t>0x05d81bcc4dc3a80e0a909b3e7fca461f800353de941a393c27bdd25ac4a5fd4d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2555,23 +2563,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.205</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TSV Hartberg</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2579,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786863668</t>
+          <t>1786867801</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2634,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20.654378</t>
+          <t>23.701493</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,7 +2667,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x1de2155e1c3ba327729349e4b0db5dcab8d6a26fc4885bf5cb6fc10388a34aac</t>
+          <t>0x74c478c25c884e128702e32231056f1f8df3fecc5378ed83072476df5090e33f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2662,17 +2678,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.205</t>
+          <t>12.65998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2683,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2728,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786863668</t>
+          <t>1786866135</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20.654378</t>
+          <t>15.462571</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,23 +2771,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
+          <t>0xd92875c7cde785279801c4010a511eb03a3411ac6a04b8a5c60708f8bfdfde3a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.09998</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2802,7 +2818,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2832,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786863582</t>
+          <t>1786865292</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>20.981571</t>
+          <t>5.028571</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,31 +2875,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
+          <t>0xb3ba12049a809b51522b33ed465df69f8887adf26be7e2a64fe1d112796b79e1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.1875</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2891,27 +2915,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2936,17 +2960,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786864292</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,28 +2987,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
+          <t>0x797638d4b1a279644b7c09a6f87d4f0bc84ed28a77802f60772f9cb336839a69</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3010,7 +3034,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3040,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,7 +3091,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
+          <t>0x1de2155e1c3ba327729349e4b0db5dcab8d6a26fc4885bf5cb6fc10388a34aac</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3078,17 +3102,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.92996</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3099,27 +3123,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3144,17 +3168,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786863030</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>66.17173</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
+          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3182,7 +3206,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>17.09998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3248,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786858705</t>
+          <t>1786863582</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3258,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>57.91411</t>
+          <t>20.981571</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3275,54 +3299,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
+          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -3330,7 +3346,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3360,7 +3376,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786858045</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3370,7 +3386,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>195.84</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,54 +3403,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
+          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -3442,7 +3450,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3472,7 +3480,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786857999</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3482,7 +3490,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>71.84466</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3499,7 +3507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
+          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3510,17 +3518,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>53.92996</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3531,27 +3539,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3576,17 +3584,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786863030</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>66.17173</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3603,7 +3611,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
+          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3614,17 +3622,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3635,27 +3643,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3680,17 +3688,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786858705</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>57.91411</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3707,23 +3715,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
+          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3731,7 +3743,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3739,27 +3755,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3784,7 +3800,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786855348</t>
+          <t>1786858045</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3794,7 +3810,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>80.645161</t>
+          <t>195.84</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3811,7 +3827,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
+          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3819,23 +3835,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.33999</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3843,27 +3867,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3888,17 +3912,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786795497</t>
+          <t>1786857999</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.425321</t>
+          <t>71.84466</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3915,7 +3939,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
+          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3923,31 +3947,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3955,27 +3971,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4000,17 +4016,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786793761</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4027,7 +4043,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
+          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4038,17 +4054,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4059,27 +4075,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4104,17 +4120,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>29.662651</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4131,28 +4147,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
+          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.68844</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4163,27 +4179,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4208,17 +4224,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786855348</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>24.608431</t>
+          <t>80.645161</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4235,7 +4251,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4243,31 +4259,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.61999</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4290,7 +4298,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4320,7 +4328,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786792979</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4330,7 +4338,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12.259241</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4347,7 +4355,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4362,22 +4370,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4402,7 +4410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4432,7 +4440,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786792948</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4442,7 +4450,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>12.240741</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4459,7 +4467,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4467,31 +4475,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786792921</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>24.587678</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4571,7 +4571,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4579,31 +4579,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12.80999</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4626,7 +4618,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4656,7 +4648,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786792918</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4666,7 +4658,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>24.57552</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4683,7 +4675,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4691,23 +4683,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4787,7 +4787,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4795,23 +4795,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4834,7 +4842,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4864,7 +4872,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4874,7 +4882,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4891,7 +4899,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4906,22 +4914,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4931,27 +4939,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4976,17 +4984,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5003,7 +5011,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5011,23 +5019,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5050,7 +5066,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5080,7 +5096,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5090,7 +5106,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5107,7 +5123,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,7 +5134,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5184,7 +5200,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5194,7 +5210,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5211,7 +5227,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5222,7 +5238,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5288,7 +5304,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5298,7 +5314,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5315,23 +5331,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5339,7 +5359,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5347,27 +5371,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5392,17 +5416,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5419,7 +5443,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5427,31 +5451,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5474,7 +5490,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5504,7 +5520,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5514,7 +5530,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,7 +5547,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5539,19 +5555,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5559,11 +5571,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5586,7 +5594,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5616,7 +5624,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5626,7 +5634,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5643,7 +5651,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5654,12 +5662,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5690,7 +5698,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5720,7 +5728,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5730,7 +5738,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5747,23 +5755,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5794,7 +5802,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5824,7 +5832,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5834,7 +5842,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5851,7 +5859,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5866,12 +5874,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5936,7 +5944,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5946,7 +5954,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,7 +5971,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5971,23 +5979,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6010,7 +6026,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6040,7 +6056,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6050,7 +6066,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6067,7 +6083,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6075,19 +6091,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6095,26 +6107,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -6122,7 +6130,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6152,7 +6160,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6162,7 +6170,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6179,7 +6187,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6190,17 +6198,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6226,7 +6234,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6256,7 +6264,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6266,7 +6274,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6283,7 +6291,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6291,23 +6299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6330,7 +6346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6360,7 +6376,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6370,7 +6386,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6387,7 +6403,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6398,12 +6414,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6464,7 +6480,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6474,7 +6490,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6491,7 +6507,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6499,23 +6515,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6538,7 +6562,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6568,7 +6592,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6578,7 +6602,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6595,28 +6619,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6642,7 +6666,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6672,7 +6696,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6682,7 +6706,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6699,27 +6723,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6727,34 +6747,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6784,7 +6800,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6794,7 +6810,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6811,62 +6827,54 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6896,7 +6904,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6906,7 +6914,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6923,39 +6931,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6963,27 +6963,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7035,39 +7035,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7090,7 +7082,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7120,7 +7112,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7130,7 +7122,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7147,12 +7139,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7162,12 +7154,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7177,7 +7169,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7187,27 +7179,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7232,17 +7224,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7259,23 +7251,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7283,7 +7279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7363,31 +7363,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7395,27 +7403,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7440,17 +7448,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7467,31 +7475,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7514,7 +7530,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7544,7 +7560,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7554,7 +7570,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7571,12 +7587,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7586,52 +7602,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7656,17 +7672,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7683,7 +7699,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7691,31 +7707,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>SC Austria Lustenau +1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7723,27 +7731,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7768,17 +7776,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7795,39 +7803,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7835,27 +7835,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7880,17 +7880,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7915,31 +7915,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7947,27 +7939,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7992,17 +7984,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8019,7 +8011,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8027,23 +8019,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8051,27 +8051,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8096,17 +8096,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8123,12 +8123,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8138,22 +8138,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8163,27 +8163,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8208,17 +8208,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8235,12 +8235,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8250,22 +8250,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8347,7 +8347,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8362,22 +8362,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8459,7 +8459,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8467,31 +8467,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8514,7 +8506,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8544,7 +8536,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8554,7 +8546,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8571,12 +8563,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8586,22 +8578,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8626,7 +8618,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8656,7 +8648,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8666,7 +8658,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8683,7 +8675,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8698,12 +8690,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8768,7 +8760,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8778,7 +8770,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8795,12 +8787,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8810,7 +8802,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8880,7 +8872,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8890,7 +8882,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8907,7 +8899,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8922,12 +8914,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8992,7 +8984,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9002,7 +8994,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9019,31 +9011,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9123,7 +9123,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9138,22 +9138,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9235,12 +9235,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9250,22 +9250,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9347,7 +9347,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9362,22 +9362,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9459,39 +9459,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -9514,7 +9506,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9544,7 +9536,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9554,7 +9546,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9571,12 +9563,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9586,12 +9578,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9656,7 +9648,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9666,7 +9658,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9683,7 +9675,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9698,12 +9690,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9768,7 +9760,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9778,7 +9770,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9795,7 +9787,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9810,7 +9802,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9880,7 +9872,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9890,7 +9882,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9907,12 +9899,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9922,22 +9914,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9962,7 +9954,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9992,7 +9984,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786704050</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10002,7 +9994,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10019,12 +10011,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10034,22 +10026,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>1.49999</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.7588</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10074,7 +10066,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10104,7 +10096,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786700992</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10114,7 +10106,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>1.976923</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10131,7 +10123,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10139,23 +10131,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786697954</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>49.083612</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10235,12 +10235,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10250,22 +10250,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>35.77998</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786696250</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>47.70664</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10347,12 +10347,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>557.83</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786696222</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>1025.894253</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,12 +10459,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10474,22 +10474,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>22.83999</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786695902</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>42.004579</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10571,27 +10571,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>296.6897</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10599,11 +10595,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -10656,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786695873</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10666,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>643.229702</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10683,12 +10675,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10698,7 +10690,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>346.54</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10768,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786695869</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10778,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>641.740741</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10795,12 +10787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10810,7 +10802,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10880,7 +10872,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786695799</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10890,7 +10882,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.851852</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10907,12 +10899,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10922,22 +10914,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10962,7 +10954,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10992,7 +10984,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786695700</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11002,7 +10994,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>1.33332</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11019,23 +11011,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>484.79999</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11043,7 +11039,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786695653</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>897.777759</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11123,102 +11123,542 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="V104" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Bundesliga/trades.xlsx
+++ b/data/sxbet/ligas/Bundesliga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x812fa3d4e263ebdb16994a6b2737919b3df2a23ada0e5a867604cbca04e1ea98</t>
+          <t>0x113d30a8d1469500028da283b49c55edb6ae2b5883ae9be3071f90f0ec8d53f2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>565.39</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SK Rapid Wien</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786888022</t>
+          <t>1786891563</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.192872</t>
+          <t>825.386861</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x00cc1ede6077ec76316a51d8963b5407eb467c5c0c211b5752bec8b449981c8f</t>
+          <t>0xeea70b07ee48d7ef22274a907f302b042d51803c6b21c3431eea9a554bea3e2f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.3938</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786887670</t>
+          <t>1786891530</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7.186441</t>
+          <t>290.539683</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe704a4356af06d75246cd4617d655ea10fbf4620e809fa4e2d8dbcf524f89ae7</t>
+          <t>0x6db3029719acb9f72c7cdbb3bdb1f44ed0e35144f0ca94f6c74c1389b4cc50e6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>224.99</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786887365</t>
+          <t>1786891362</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20.901961</t>
+          <t>762.677966</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,27 +859,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3042c7a60b1ec4ef2d88e5ecc7a771ba0a2dd47f415b018e857ba99cab944459</t>
+          <t>0xa3c0769104e55222d9c28ee9aef39b234d57f4e7bcadf6b9bf3b6bee6cd8f48a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>233.90994</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -887,11 +883,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786886556</t>
+          <t>1786891230</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>58.169492</t>
+          <t>265.80675</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xda8cf2ddfe903270bba7449c2f7bf9acbc33b05eac7a7431fb09e9ee64853f08</t>
+          <t>0x1c8b88956852b2c72e5f52c0e8a48e639896f83a574f3f391aaa54d38769080b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,12 +974,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>229.82999</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1048,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786882671</t>
+          <t>1786891154</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>370.693532</t>
+          <t>8.048</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,23 +1067,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x81f5b415be2d9f364b502493091c0350e0da5326ca647b3480b14b2bb1c334fb</t>
+          <t>0xd05b43f566ec0ea8770277860c72a35b2624302e88613e5b79374b6675ca22f6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00422</t>
+          <t>454.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1107,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786878747</t>
+          <t>1786890979</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>726.48</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf3bc0100004de3bde89c6fd3055ba5bd9878df9155f316db14ec34daf9886062</t>
+          <t>0x55c216fb57d48f41b21f1ced4f45b1dc622f472efc539180a46cbb5064a31ee8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,12 +1182,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.56997</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1211,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786877644</t>
+          <t>1786890960</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>68.15659</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xef05d2408f42aecc4b2a6cf4b72c3ef0cd01f9213fe2a25ca0dfa829110934ff</t>
+          <t>0x436f9877e2569896697e306259fff5ac7882ca7ceb7a1110c243d2929fad6260</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1294,12 +1286,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>57.83997</t>
+          <t>130.53998</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.6687</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1315,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786877501</t>
+          <t>1786890613</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>69.686711</t>
+          <t>195.19997</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,28 +1379,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9ff5d2cde067c6ad242419d3d9bdbaf418ce158b1f50ec823b76bb08b5b0f34f</t>
+          <t>0xb561da5a8a6ba15890a8cead5fee5d8cc573a1aeef03b668b8ec2360d6ae1d3a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1434,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0x64c7579a28126920f5e3886605cd35d6c5bbd05aa023bac7e184c6d16eb62ffd</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786876123</t>
+          <t>1786890592</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.793017</t>
+          <t>243.168627</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,28 +1483,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x45639b4a3510d9a1f0dc1a3c57bd5c2c43f6011c9a4874e4291a0f1361f866fc</t>
+          <t>0x053ce65dec3d2e8abadcca632968056546d1eff5e09460dc2958598fabe0e9b3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>591.4</t>
+          <t>3.81998</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6687</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786876048</t>
+          <t>1786889737</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1179.850374</t>
+          <t>5.71212</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,23 +1587,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xfe72d608227d2615a1b90aefefca2cbbb3e0ff5a0061bb2df632410a9f0f9530</t>
+          <t>0xf4392a5a3d7dcc1a54a824d283142fc7088c36148fd6daa52754f9f90729484e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.6687</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1627,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786872056</t>
+          <t>1786889724</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>54.715152</t>
+          <t>11.439252</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,23 +1691,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb84c412ef91494a7066f12271852db25d63c75af7c1e9b26e57ed1c4991acec5</t>
+          <t>0x0f82346fc464d838718989e23f864baa97025724cbe25357f07ff7b267af9e25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>1322.39406</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4238</t>
+          <t>1.8725</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1731,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786870513</t>
+          <t>1786889627</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>94.348083</t>
+          <t>1515.637891</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,28 +1795,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2f524160a862509b29112385fcf72a4688928c84e4aaf6160e6762e112dafd6d</t>
+          <t>0xa5a71334945ac9a7eb0acd457a297aa9c9b44740c6631110469b320666e63292</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>900.5</t>
+          <t>215.75994</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1850,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1880,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786870469</t>
+          <t>1786889626</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1796.508728</t>
+          <t>247.644121</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,28 +1899,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x43b6ea29196f2fdd23ccb2434b2a5c2303cbddc27e7b9ab1393a2c1d934e15db</t>
+          <t>0xb2b9d2627bda762dad0c09233f03dd0d363488887548f00bc5b916f9dd160ab6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>130.29</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1939,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SK Rapid Wien</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19729742</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786870403</t>
+          <t>1786889039</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>310.214286</t>
+          <t>49.709924</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +2003,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3e487ada34f8a35d4e11d554823d4747f6bacd7acbc906a4760553dcccc48e20</t>
+          <t>0x6c5a802e02caa584c47cdec162ef88ac8e503d083cd7dd58dbe992ef708238ba</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2019,19 +2011,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>208.96639</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2039,11 +2027,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2066,7 +2050,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xe871719b5fd77c56cc970200624c2bdc63c0892cbbb3c746da8dd2228878d10d</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2096,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786870403</t>
+          <t>1786888992</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>153.55102</t>
+          <t>515.966395</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,12 +2107,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5fdca699fdb043ee4eed8313b2eba1678a243ef8458326568b7e2b202efe6fb1</t>
+          <t>0x812fa3d4e263ebdb16994a6b2737919b3df2a23ada0e5a867604cbca04e1ea98</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x161ba9aad05022c88726A1D1244fDF624e51BFD5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2138,12 +2122,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2153,7 +2137,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2163,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786869580</t>
+          <t>1786888022</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6.179104</t>
+          <t>4.192872</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7e0b4b4cd37a32b012ae08e8fafc2a2c8bc292701e823cf78c0980f92bc7a1c0</t>
+          <t>0x00cc1ede6077ec76316a51d8963b5407eb467c5c0c211b5752bec8b449981c8f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2243,15 +2227,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.08996</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2259,7 +2247,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -2267,27 +2259,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2312,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786868988</t>
+          <t>1786887670</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.335151</t>
+          <t>7.186441</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,7 +2331,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x21823d634d9b05dcf49935cd5a225282d8f45e2f2bbb6cbd1e8fdfeb74e09dae</t>
+          <t>0xe704a4356af06d75246cd4617d655ea10fbf4620e809fa4e2d8dbcf524f89ae7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,17 +2342,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.64999</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2371,27 +2363,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TSV Hartberg</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FK Austria Wien</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19729521</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786868846</t>
+          <t>1786887365</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10.72579</t>
+          <t>20.901961</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,12 +2435,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x765333b5d50950a47c39ac8b8b82009e8a312c78991c1a5c77c6c4f06f399d84</t>
+          <t>0x3042c7a60b1ec4ef2d88e5ecc7a771ba0a2dd47f415b018e857ba99cab944459</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2458,12 +2450,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2473,24 +2465,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TSV Hartberg vs FK Austria Wien</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>TSV Hartberg</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>TSV Hartberg</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>FK Austria Wien</t>
@@ -2498,7 +2490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
+          <t>0xd934db9b173b88dabd02fc2d6994ceb46c47f84c0655b9d60e56d11d70f19027</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2528,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786867972</t>
+          <t>1786886556</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>33.044776</t>
+          <t>58.169492</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,7 +2547,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x05d81bcc4dc3a80e0a909b3e7fca461f800353de941a393c27bdd25ac4a5fd4d</t>
+          <t>0xda8cf2ddfe903270bba7449c2f7bf9acbc33b05eac7a7431fb09e9ee64853f08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2563,19 +2555,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>229.82999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2583,26 +2571,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TSV Hartberg vs FK Austria Wien</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>TSV Hartberg</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>TSV Hartberg vs FK Austria Wien</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>TSV Hartberg</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>FK Austria Wien</t>
@@ -2610,7 +2594,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2624,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786867801</t>
+          <t>1786882671</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2634,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>23.701493</t>
+          <t>370.693532</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,23 +2651,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x74c478c25c884e128702e32231056f1f8df3fecc5378ed83072476df5090e33f</t>
+          <t>0x81f5b415be2d9f364b502493091c0350e0da5326ca647b3480b14b2bb1c334fb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.65998</t>
+          <t>1.00422</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8188</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2714,7 +2698,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786866135</t>
+          <t>1786878747</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15.462571</t>
+          <t>2.391</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,23 +2755,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd92875c7cde785279801c4010a511eb03a3411ac6a04b8a5c60708f8bfdfde3a</t>
+          <t>0xf3bc0100004de3bde89c6fd3055ba5bd9878df9155f316db14ec34daf9886062</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>56.56997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4375</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2818,7 +2802,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2848,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786865292</t>
+          <t>1786877644</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2858,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5.028571</t>
+          <t>68.15659</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,27 +2859,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb3ba12049a809b51522b33ed465df69f8887adf26be7e2a64fe1d112796b79e1</t>
+          <t>0xef05d2408f42aecc4b2a6cf4b72c3ef0cd01f9213fe2a25ca0dfa829110934ff</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57.83997</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.1875</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2903,31 +2883,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien vs Grazer AK</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SK Rapid Wien</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Grazer AK</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>SK Rapid Wien vs Grazer AK</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>SK Rapid Wien</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Grazer AK</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
@@ -2960,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786864292</t>
+          <t>1786877501</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>69.686711</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,23 +2963,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x797638d4b1a279644b7c09a6f87d4f0bc84ed28a77802f60772f9cb336839a69</t>
+          <t>0x9ff5d2cde067c6ad242419d3d9bdbaf418ce158b1f50ec823b76bb08b5b0f34f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.205</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3064,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786863668</t>
+          <t>1786876123</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3074,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>20.654378</t>
+          <t>2.793017</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,28 +3067,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1de2155e1c3ba327729349e4b0db5dcab8d6a26fc4885bf5cb6fc10388a34aac</t>
+          <t>0x45639b4a3510d9a1f0dc1a3c57bd5c2c43f6011c9a4874e4291a0f1361f866fc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.205</t>
+          <t>591.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3138,7 +3114,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3144,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786863668</t>
+          <t>1786876048</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3154,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>20.654378</t>
+          <t>1179.850374</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,7 +3171,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
+          <t>0xfe72d608227d2615a1b90aefefca2cbbb3e0ff5a0061bb2df632410a9f0f9530</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3206,12 +3182,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17.09998</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3272,7 +3248,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786863582</t>
+          <t>1786872056</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3258,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20.981571</t>
+          <t>54.715152</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,28 +3275,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
+          <t>0xb84c412ef91494a7066f12271852db25d63c75af7c1e9b26e57ed1c4991acec5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.4238</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3331,27 +3307,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3376,17 +3352,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786870513</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>94.348083</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,28 +3379,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
+          <t>0x2f524160a862509b29112385fcf72a4688928c84e4aaf6160e6762e112dafd6d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>900.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3450,7 +3426,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3480,7 +3456,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786863174</t>
+          <t>1786870469</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3466,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>277.136259</t>
+          <t>1796.508728</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,7 +3483,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
+          <t>0x43b6ea29196f2fdd23ccb2434b2a5c2303cbddc27e7b9ab1393a2c1d934e15db</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3518,12 +3494,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>53.92996</t>
+          <t>130.29</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3554,7 +3530,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3584,7 +3560,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786863030</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3594,7 +3570,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>66.17173</t>
+          <t>310.214286</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3611,7 +3587,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
+          <t>0x3e487ada34f8a35d4e11d554823d4747f6bacd7acbc906a4760553dcccc48e20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3619,15 +3595,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3635,7 +3615,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -3658,7 +3642,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
+          <t>0xe871719b5fd77c56cc970200624c2bdc63c0892cbbb3c746da8dd2228878d10d</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3688,7 +3672,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786858705</t>
+          <t>1786870403</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3698,7 +3682,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>57.91411</t>
+          <t>153.55102</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3715,7 +3699,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
+          <t>0x5fdca699fdb043ee4eed8313b2eba1678a243ef8458326568b7e2b202efe6fb1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3730,12 +3714,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3745,7 +3729,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3755,27 +3739,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3800,7 +3784,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786858045</t>
+          <t>1786869580</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3794,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>195.84</t>
+          <t>6.179104</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,7 +3811,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
+          <t>0x7e0b4b4cd37a32b012ae08e8fafc2a2c8bc292701e823cf78c0980f92bc7a1c0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3835,19 +3819,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>2.08996</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.895</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3855,26 +3835,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>WSG Tirol</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>WSG Tirol</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>FC Red Bull Salzburg</t>
@@ -3912,7 +3888,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786857999</t>
+          <t>1786868988</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3922,7 +3898,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>71.84466</t>
+          <t>2.335151</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,7 +3915,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
+          <t>0x21823d634d9b05dcf49935cd5a225282d8f45e2f2bbb6cbd1e8fdfeb74e09dae</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3950,17 +3926,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>6.64999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3971,27 +3947,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4016,7 +3992,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786868846</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4026,7 +4002,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>10.72579</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4043,7 +4019,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
+          <t>0x765333b5d50950a47c39ac8b8b82009e8a312c78991c1a5c77c6c4f06f399d84</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4051,23 +4027,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>TSV Hartberg</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4075,27 +4059,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>WSG Tirol vs FC Red Bull Salzburg</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>WSG Tirol</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>FC Red Bull Salzburg</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19729744</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4120,7 +4104,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786857876</t>
+          <t>1786867972</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4130,7 +4114,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>75.21197</t>
+          <t>33.044776</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4147,23 +4131,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
+          <t>0x05d81bcc4dc3a80e0a909b3e7fca461f800353de941a393c27bdd25ac4a5fd4d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4171,7 +4159,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TSV Hartberg</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4194,7 +4186,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
+          <t>0xc0e470a6f985b40857b98d0bf1e72c7493f5d62156b7494110164d161a3d2123</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4224,7 +4216,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786855348</t>
+          <t>1786867801</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4234,7 +4226,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>80.645161</t>
+          <t>23.701493</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4251,7 +4243,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
+          <t>0x74c478c25c884e128702e32231056f1f8df3fecc5378ed83072476df5090e33f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4262,17 +4254,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.33999</t>
+          <t>12.65998</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.8188</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4283,27 +4275,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4328,17 +4320,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786795497</t>
+          <t>1786866135</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.425321</t>
+          <t>15.462571</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4355,27 +4347,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
+          <t>0xd92875c7cde785279801c4010a511eb03a3411ac6a04b8a5c60708f8bfdfde3a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4383,11 +4371,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4395,27 +4379,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdbdb28c6eda6dd3731d4bd1492768856d41868a3733615b06652a75fb151c3ea</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4440,17 +4424,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786793761</t>
+          <t>1786865292</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>5.028571</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4467,23 +4451,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
+          <t>0xb3ba12049a809b51522b33ed465df69f8887adf26be7e2a64fe1d112796b79e1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.1875</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4491,7 +4479,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4499,27 +4491,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4544,17 +4536,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786864292</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>29.662651</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4571,7 +4563,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
+          <t>0x797638d4b1a279644b7c09a6f87d4f0bc84ed28a77802f60772f9cb336839a69</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4582,17 +4574,17 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.68844</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4603,27 +4595,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4648,17 +4640,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786793038</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>24.608431</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4675,7 +4667,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
+          <t>0x1de2155e1c3ba327729349e4b0db5dcab8d6a26fc4885bf5cb6fc10388a34aac</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4683,31 +4675,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6.61999</t>
+          <t>11.205</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4715,27 +4699,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4760,17 +4744,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786792979</t>
+          <t>1786863668</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12.259241</t>
+          <t>20.654378</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4787,7 +4771,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
+          <t>0x2dc2577fbc6c36da9ae0856cda789563826413926f37251d7767d2a38dbd5858</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4795,31 +4779,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>17.09998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4827,27 +4803,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4872,17 +4848,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786792948</t>
+          <t>1786863582</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>12.240741</t>
+          <t>20.981571</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4899,39 +4875,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
+          <t>0x94bb64403aea1a46e1c92c43c5ea64f6d045a22d6cca4a76d6dbda1041590ccd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -4939,27 +4907,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4984,17 +4952,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786792921</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>24.587678</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5011,39 +4979,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
+          <t>0x7d29c2a70e1afa1d242ea36ab878a09fce26d4265e6db4179f7fd0d7b1b01cd1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12.80999</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5051,27 +5011,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5096,17 +5056,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786792918</t>
+          <t>1786863174</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>24.57552</t>
+          <t>277.136259</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5123,7 +5083,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
+          <t>0x59652a1114ce6ef4a12345232c064354f2986f15df55eab4edbc771d3de0b6c8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5134,12 +5094,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53.92996</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5155,27 +5115,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5200,17 +5160,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786788191</t>
+          <t>1786863030</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>23.809524</t>
+          <t>66.17173</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5227,7 +5187,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
+          <t>0x7b26930107bf7e572e91b471ded8e2a18bb1517e1c1adee69605f6b67a41b21f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5238,12 +5198,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5259,27 +5219,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SK Rapid Wien vs Grazer AK</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SK Rapid Wien</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xb3640d3b859ee1a658dfdbd2644b82028763b4ee685341873962554c8857d8c5</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729742</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5304,17 +5264,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786784805</t>
+          <t>1786858705</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>57.91411</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5331,7 +5291,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
+          <t>0x5ef17795326a825ccefc3f4a03d6349b0a520f97716ef3207ae723b3c40fe45b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5346,12 +5306,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5361,7 +5321,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5371,27 +5331,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5416,17 +5376,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786784759</t>
+          <t>1786858045</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>9.245283</t>
+          <t>195.84</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5443,7 +5403,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
+          <t>0x5f7edc52d345896639c8bafe92271f8bd6bd089dd2b612cdf81ca27634ca81df</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5451,15 +5411,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5467,7 +5431,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>WSG Tirol</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5475,27 +5443,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x76ea0099aaba549cd5594c5198b1af0f10b873faa8b30b7509dbcd6b16f059c3</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5520,17 +5488,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786784496</t>
+          <t>1786857999</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>7.285714</t>
+          <t>71.84466</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5547,7 +5515,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
+          <t>0xbaad7f661458d0769d5227ab571043bd64c85ff37f72c93fe19ec0c11a9e9c30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5558,17 +5526,17 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5579,27 +5547,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0xee8918d2ad615b94e1d2bcf86994ce8f2007035e382ee8df2bc33f88b8b43aed</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5624,17 +5592,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786783823</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>300.309524</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5651,7 +5619,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
+          <t>0x31e5890e230df1a4bf557e37f35bd8198ca66587d7ecb11e4e384c7826f3285f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5662,17 +5630,17 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5683,27 +5651,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>WSG Tirol vs FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>WSG Tirol</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FC Red Bull Salzburg</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x2eea38608fb77e62451ea105f97839611e88576d37749e99a8cb671b29eef206</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729744</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5728,17 +5696,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786783809</t>
+          <t>1786857876</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>59.285714</t>
+          <t>75.21197</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5755,23 +5723,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
+          <t>0x89e7b81b59a1ec8a8341fd3184cc580959059aec3e2949e93ac58092865c2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5787,27 +5755,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>TSV Hartberg vs FK Austria Wien</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>TSV Hartberg</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>FK Austria Wien</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x7a313dea68fce5b0456ab72c92139c7dad3d9c8bfeb765e94e9ac755635e4569</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19729521</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5832,17 +5800,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786781668</t>
+          <t>1786855348</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.325581</t>
+          <t>80.645161</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5859,7 +5827,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
+          <t>0x65215b0f9cfd7578b2dec42dbd0c2f2da3cc5297c7a349e2cfb13e3fec5efe10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5867,31 +5835,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13.53999</t>
+          <t>1.33999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5737</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -5914,7 +5874,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5944,7 +5904,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786781558</t>
+          <t>1786795497</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5954,7 +5914,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>23.599111</t>
+          <t>2.425321</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5971,7 +5931,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
+          <t>0xce2efdc8f513366d77ab30f5cdd223138aeb77cd0164c87d014f04bec3edf71b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5986,12 +5946,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6001,7 +5961,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6026,7 +5986,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6056,7 +6016,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786781557</t>
+          <t>1786793761</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6066,7 +6026,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>372.0</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6083,7 +6043,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
+          <t>0x406d81bdebc96ce2163f0a7de8ce8db9a3adfa0d13007da98f4bc40daba28c16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6094,12 +6054,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16.70545</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6130,7 +6090,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6160,7 +6120,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786781556</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6170,7 +6130,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>20.24903</t>
+          <t>29.662651</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6187,7 +6147,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
+          <t>0x1b0e20a2feb7f1c97a034929367634fa2ef7dccaa82934256aacc9fb4796a484</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6198,17 +6158,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>13.68844</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6234,7 +6194,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6264,7 +6224,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786793038</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6274,7 +6234,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>337.5</t>
+          <t>24.608431</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6291,7 +6251,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
+          <t>0xb431fe28843c77f1e88e6947cd1f27cbc5c43b162133fb4291042fe066b8a355</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6306,22 +6266,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14.00999</t>
+          <t>6.61999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz -0.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6346,7 +6306,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6376,7 +6336,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786792979</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6386,7 +6346,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>24.57893</t>
+          <t>12.259241</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6403,7 +6363,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
+          <t>0x5c5694523226185142ffe23dbc305ae30a85fd1e6d9f32c2eb8b86707b2385a1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6411,23 +6371,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>947.06589</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6450,7 +6418,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6480,7 +6448,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786781541</t>
+          <t>1786792948</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6490,7 +6458,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1647.071113</t>
+          <t>12.240741</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6507,7 +6475,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
+          <t>0xe7ea6bec5032103644784b93ddc39d72a547e6d86595a168aab2a1693dd717fd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6522,39 +6490,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>125.04</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -6562,7 +6530,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6592,7 +6560,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786781540</t>
+          <t>1786792921</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6602,7 +6570,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>219.368421</t>
+          <t>24.587678</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6619,7 +6587,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
+          <t>0xaa275b4eca0d379fd10466aee405a9542631db9b3d40b2c7dd1a0af91fdfe0d2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6627,23 +6595,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>12.80999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6666,7 +6642,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0x6aaf5db6a1d0314e9e290edb167c8edc781182e2533868e6b8f8b42156d26bbf</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6696,7 +6672,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786781537</t>
+          <t>1786792918</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6706,7 +6682,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>117.634783</t>
+          <t>24.57552</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6723,7 +6699,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
+          <t>0x8f894e79d36f8f911cd4d3a8e818e17d973c0473b68c0a0d4cfd6c470f571a1d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6734,12 +6710,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>180.40541</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6800,7 +6776,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786781080</t>
+          <t>1786788191</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6810,7 +6786,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>405.405416</t>
+          <t>23.809524</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6827,7 +6803,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
+          <t>0x929bcf770047be144c6109f36995d3484455f4705399b2ba419216b42f701a36</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6838,17 +6814,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6874,7 +6850,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6904,7 +6880,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786784805</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6914,7 +6890,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6931,7 +6907,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
+          <t>0xb2b369362653f3892b793c5c80c318ce72777bda2be37728756ebe16efa2f99d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6939,23 +6915,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7.955</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SC Austria Lustenau</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -6963,27 +6947,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
+          <t>0xfd00473152becb9b8f7e4c66bcd41612365f137909414870a08b84bfde56a5dc</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19729749</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7008,17 +6992,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786780504</t>
+          <t>1786784759</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>15.11639</t>
+          <t>9.245283</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7035,23 +7019,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
+          <t>0xc52f719e5e3dedc2d577bad559c04d3f8f6263c498e25a87a9880102bcfe6e02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7112,7 +7096,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786780420</t>
+          <t>1786784496</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7122,7 +7106,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>340.73913</t>
+          <t>7.285714</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7139,27 +7123,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
+          <t>0xaf62b889127226622be94fcc8bb32ca013efd42926b037e3bcba28eeb6a8d147</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>126.13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7167,34 +7147,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7224,7 +7200,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786780419</t>
+          <t>1786783823</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7234,7 +7210,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>300.309524</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7251,27 +7227,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
+          <t>0x48a35fa13ba04a35518208e175601d5a4540372bcb7c3884cd0e778e0caa7918</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7279,34 +7251,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>SCR Altach</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>SCR Altach</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7336,7 +7304,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786780410</t>
+          <t>1786783809</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7346,7 +7314,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>390.243902</t>
+          <t>59.285714</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7363,27 +7331,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
+          <t>0x0fc48e6e97911901375a6e93565108f92583c2b7b39184a31b6099fcfcdeda24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7391,11 +7355,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7403,27 +7363,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7448,17 +7408,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786780232</t>
+          <t>1786781668</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>351.824561</t>
+          <t>2.325581</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7475,12 +7435,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
+          <t>0xeded193d82b037ab9ff58f59af24e4987be491e6c2fc32ce9266fee00eccba4a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7490,12 +7450,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>13.53999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.5737</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7560,7 +7520,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786779370</t>
+          <t>1786781558</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7570,7 +7530,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>59.624714</t>
+          <t>23.599111</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7587,12 +7547,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
+          <t>0xe03f8e1d89b975d00524d7d3c3e8d30ce9016c71a8d61dd41eaa4cdd7ef723e2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7602,12 +7562,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7617,7 +7577,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7627,27 +7587,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7672,17 +7632,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786779234</t>
+          <t>1786781557</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>129.708108</t>
+          <t>372.0</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7699,7 +7659,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
+          <t>0x6ab18c3d6ad4480863951529a2f24c02bdf99654924908b7a1c5e0003813c335</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7710,12 +7670,12 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>16.70545</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7746,7 +7706,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7776,7 +7736,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786769573</t>
+          <t>1786781556</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7786,7 +7746,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>132.596685</t>
+          <t>20.24903</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7803,7 +7763,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
+          <t>0x883c03e6e37ba2928ba8187def6e2d23fff87b9c42e64391853f92cd2b807301</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7814,17 +7774,17 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7850,7 +7810,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
+          <t>0x7d6afaf8e2eb0de516228f14d3347f326155bbd184f5f4e552904aabedd1f399</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7880,7 +7840,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786769552</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7890,7 +7850,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>29.850746</t>
+          <t>337.5</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7907,7 +7867,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
+          <t>0x66b1b520bc3067b9c082aab24f68da6a8de0928517f5a640155b3684438b6d4f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7915,23 +7875,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.99996</t>
+          <t>14.00999</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -7954,7 +7922,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7984,7 +7952,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786743606</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7994,7 +7962,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1.208411</t>
+          <t>24.57893</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8011,7 +7979,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
+          <t>0x3e5d3273b1522224dcafb87b032cf777a12abee1268073765664567f8102301c</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8019,46 +7987,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>947.06589</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>SK Puntigamer Sturm Graz</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>SCR Altach</t>
@@ -8066,7 +8026,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8096,7 +8056,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786742639</t>
+          <t>1786781541</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8106,7 +8066,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>48.978512</t>
+          <t>1647.071113</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8123,7 +8083,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
+          <t>0xb8541fcb93a70e4f74ed43167dc8888f15ccf124df2801ec678a3555aa345f9a</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8138,22 +8098,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>125.04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7063</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau +1</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8163,27 +8123,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau vs Wolfsberger AC</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>SC Austria Lustenau</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19733157</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8208,17 +8168,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786735874</t>
+          <t>1786781540</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786806000</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.415901</t>
+          <t>219.368421</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8235,27 +8195,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
+          <t>0xb59fef6b58a7af410c1d57b2ce43374b8435fa0117b4dba90e2205374d589a1d</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>26.06999</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8263,11 +8219,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8275,27 +8227,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8320,17 +8272,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786716750</t>
+          <t>1786781537</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>47.61642</t>
+          <t>117.634783</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8347,7 +8299,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
+          <t>0x8eb515531d108c8c89a4f54e9080921b3b503361b6333094f86f0991ecc4230c</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8355,31 +8307,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>66.68</t>
+          <t>180.40541</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8387,27 +8331,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8432,17 +8376,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786714580</t>
+          <t>1786781080</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>134.707071</t>
+          <t>405.405416</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8459,7 +8403,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
+          <t>0xc5af80a94df42663837e0b5630b08dda178afe85c20a309056a0110961087ef2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8470,17 +8414,17 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8491,27 +8435,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
+          <t>0x5aa821b44042abcbe7ef9cc770872965f5d8f3cad2bcddf82f2f1b1f22d6b87b</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8536,17 +8480,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786714022</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>49.088</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8563,39 +8507,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
+          <t>0xa02211098f9e0e9cde92da89a1549f244d82dcf8b4e237a95f82c19fe9d0111d</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.955</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8603,27 +8539,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8648,17 +8584,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786713936</t>
+          <t>1786780504</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>13.95443</t>
+          <t>15.11639</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8675,39 +8611,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
+          <t>0xcfdf70561ef55ea79db1fb367ef310d31d5f611aa367536e963ed1b549160d61</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.76999</t>
+          <t>156.74</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>LASK Linz -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -8715,27 +8643,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8760,17 +8688,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786712107</t>
+          <t>1786780420</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2.681803</t>
+          <t>340.73913</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8787,12 +8715,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
+          <t>0x51ce843a81fbbb469427410348578cdf84a6cf08f110fbdb330af0301c5c9d59</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8802,22 +8730,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2515.19</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8827,27 +8755,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8872,17 +8800,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786711888</t>
+          <t>1786780419</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>4625.636782</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8899,12 +8827,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
+          <t>0x43ab6823b5405fe2a63124b46419923fbc86a11ef1276f93107f5168e5691bca</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8914,22 +8842,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8939,27 +8867,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8984,17 +8912,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786710267</t>
+          <t>1786780410</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>48.258661</t>
+          <t>390.243902</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9011,12 +8939,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
+          <t>0x767b830b6b9e20e2b8970dde90f703e756ca9dfb90b723db864e5d7bded0e241</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9026,22 +8954,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>100.27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9051,27 +8979,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x2c1dfe8f7d95e6aab7074259c7a84858e4bb36b57d078d41fdeb8293c1b9d1af</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9096,17 +9024,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786709725</t>
+          <t>1786780232</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>41.011494</t>
+          <t>351.824561</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9123,12 +9051,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
+          <t>0xa945b666ece1f6956bc961935877313c49ba276442c14df4984ce37b40e1260a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9138,12 +9066,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9153,7 +9081,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LASK Linz -0.5</t>
+          <t>SK Puntigamer Sturm Graz -0.5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9163,27 +9091,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
+          <t>0x36a76d58e9231e3dd642f9251390e1208b0d957b9aa4aba2d9cb4086412e39f3</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9208,17 +9136,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786709683</t>
+          <t>1786779370</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>3.493384</t>
+          <t>59.624714</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9235,7 +9163,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
+          <t>0x0d3acbb1f8c7e72a93db5b071fa7236857d3dc3a4d12223383cf472db18b7e29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9250,22 +9178,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>91.41</t>
+          <t>59.99</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9275,27 +9203,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xd8ede877239899bf938c89c412c9439bf1da6aecd86d8b9ed30f9dde6eb6cde8</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9320,17 +9248,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786706976</t>
+          <t>1786779234</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>168.110345</t>
+          <t>129.708108</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9347,7 +9275,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
+          <t>0xc6d2a8b853b5450aa412843cb679453d847a77da5c64a0224bb149251893d5ff</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9355,31 +9283,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -9387,27 +9307,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xdc757481a8a8ac864d99e3b4e23fba9406b88654e49f3b581336a135e69318d0</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9432,17 +9352,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786705939</t>
+          <t>1786769573</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>6.635945</t>
+          <t>132.596685</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9459,28 +9379,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
+          <t>0xce5fff94a655b2cdbb41d25d6a81cf122f52ea3c120ae800cc043a34a5db9c7a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>228.48997</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.8613</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -9491,27 +9411,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
+          <t>0x6954ef56223b5a43400e053a1675e04b88b62ca56558724cf0f6ed80166863d4</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9536,17 +9456,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786704847</t>
+          <t>1786769552</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>265.300401</t>
+          <t>29.850746</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9563,7 +9483,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
+          <t>0xd45786b98ae91370804a2c736206ead39e1fbca9cc23313580a6460ce8890120</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9571,31 +9491,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>0.99996</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -9603,27 +9515,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x67081e39b5bdafac1f6e73bfb5b6ad7f5270717f800f67f430d126b0012152be</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9648,17 +9560,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786704771</t>
+          <t>1786743606</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>1.208411</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9675,7 +9587,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
+          <t>0xe3673179171948d22973056f2b65336938ec2bd74178551590fae764681a32b0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9690,22 +9602,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9715,27 +9627,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SK Puntigamer Sturm Graz vs SCR Altach</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x9ad9bbce76c9cbd30662e8a4ab5c3452c8c358a613fd72a50c8b7181dc33fd63</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19729749</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9760,17 +9672,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786704503</t>
+          <t>1786742639</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>48.978512</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9787,7 +9699,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
+          <t>0x8daa66082122677c89c3970f2fc64caee62b6057e931a200df421be096656432</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9802,22 +9714,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7063</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>SC Austria Lustenau +1</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9827,27 +9739,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LASK Linz vs SV Ried</t>
+          <t>SC Austria Lustenau vs Wolfsberger AC</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SC Austria Lustenau</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xba0ea7711f0d7bcf759821de108afa2d44f1e764dbb51fedf4086a71d5aeb317</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19722986</t>
+          <t>L19733157</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9872,17 +9784,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786704472</t>
+          <t>1786735874</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1786728600</t>
+          <t>1786806000</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>1.415901</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9899,12 +9811,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+          <t>0x54c3e231f8760e93b735c3aad70b0f6d9bf290f79601bb3e545369171a42f0a6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9914,22 +9826,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>26.06999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9954,7 +9866,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9984,7 +9896,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786704050</t>
+          <t>1786716750</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9994,7 +9906,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>47.61642</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10011,12 +9923,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+          <t>0x0221ccc43787d77e6f9bc6e244999aa02abe58f4c73f1e3e86f8c053ab060c42</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10026,22 +9938,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.49999</t>
+          <t>66.68</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.7588</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10066,7 +9978,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10096,7 +10008,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786700992</t>
+          <t>1786714580</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10106,7 +10018,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1.976923</t>
+          <t>134.707071</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10123,7 +10035,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+          <t>0xa45e722b2f8857d69d73317ce3084dc2e69df0903bf371409451731203c676d2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10131,31 +10043,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -10178,7 +10082,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x154b733171c7f01e7789a18e341fb6e3e8121f02e74e4febf14af52e6bd870fc</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10208,7 +10112,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786697954</t>
+          <t>1786714022</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10218,7 +10122,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>49.083612</t>
+          <t>49.088</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10235,12 +10139,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+          <t>0x8c91335ae9ec2badc857e675d35ff8e3818eb0b802c3d05fc3ebf796c3f18195</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10250,22 +10154,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>35.77998</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10290,7 +10194,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0xd395255f1fdaa1f3bea5a106e2055834680bdee9a58a41895c7a38f31f80beae</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10320,7 +10224,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786696250</t>
+          <t>1786713936</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10330,7 +10234,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>47.70664</t>
+          <t>13.95443</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10347,12 +10251,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+          <t>0xd55646b617b0f28d4b7c8f4a7157567db85abf92b455bd498870f96fbaeb125a</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10362,22 +10266,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>557.83</t>
+          <t>1.76999</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10402,7 +10306,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10432,7 +10336,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786696222</t>
+          <t>1786712107</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10442,7 +10346,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1025.894253</t>
+          <t>2.681803</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,12 +10363,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+          <t>0xc63dfc3e1f7d71137952fe723ef12e4c36bed56f14b5b69b20f56f7c04cb9fb1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10474,7 +10378,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>22.83999</t>
+          <t>2515.19</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10544,7 +10448,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786695902</t>
+          <t>1786711888</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10554,7 +10458,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>42.004579</t>
+          <t>4625.636782</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10571,7 +10475,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+          <t>0x2bcb64c2bfd3514856c15034bf37585fb056e6d201e48aa560646e765f2bf612</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10579,15 +10483,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>296.6897</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10595,7 +10503,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -10648,7 +10560,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786695873</t>
+          <t>1786710267</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10658,7 +10570,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>643.229702</t>
+          <t>48.258661</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10675,12 +10587,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+          <t>0xbc037195afbbb894f93552f09a96dbf26e085b032162fd371bdcd6e507cc6030</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10690,12 +10602,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>346.54</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10760,7 +10672,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786695869</t>
+          <t>1786709725</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10770,7 +10682,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>641.740741</t>
+          <t>41.011494</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10787,12 +10699,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+          <t>0x8bb6ce50f9cdd747617cc6ddd8923bac84c636a43b5747ece36118588d661e56</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10802,22 +10714,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>LASK Linz -0.5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10842,7 +10754,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x8ed613eccc85721e5128096540f9355a0f8cf59e645c356e533ccd8eb1928ec5</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10872,7 +10784,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786695799</t>
+          <t>1786709683</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10882,7 +10794,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1.851852</t>
+          <t>3.493384</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10899,12 +10811,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+          <t>0x2d42370b05751a34d03be1367afb327b6e72ae3b341fa63651c557748608e06f</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10914,22 +10826,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>91.41</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>LASK Linz -1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10954,7 +10866,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10984,7 +10896,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786695700</t>
+          <t>1786706976</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10994,7 +10906,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1.33332</t>
+          <t>168.110345</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11011,12 +10923,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+          <t>0x078ea10216f3741d1757134ccf5904d995bb1b31fb4dda2433595eacd7c26ca8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11026,12 +10938,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>484.79999</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11096,7 +11008,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786695653</t>
+          <t>1786705939</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11106,7 +11018,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>897.777759</t>
+          <t>6.635945</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11123,39 +11035,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+          <t>0x89225b7389497635b7a6d5762e0312ef71ce7e6aad4bacb31d914cb8e8063156</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>228.48997</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.8613</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>LASK Linz -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -11178,7 +11082,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0xe385ab4b9eeee1b6ee91ce4a2452c903e1102819fc6a3ef47b0b71ecca4789e7</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11208,7 +11112,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786695037</t>
+          <t>1786704847</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11218,7 +11122,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>265.300401</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11235,12 +11139,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+          <t>0x798a2a121340304c054e489a82c2fbcbbacbb2b5a10fac5eccae9d0e6f953242</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11250,22 +11154,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11290,7 +11194,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11320,7 +11224,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786694953</t>
+          <t>1786704771</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11330,7 +11234,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11347,12 +11251,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+          <t>0xd7c7ed5aee6d42691c0cdba24cc2a4844a2148619b251e896e222af12c3f399a</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11362,22 +11266,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>LASK Linz -1</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11402,7 +11306,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11432,7 +11336,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786694900</t>
+          <t>1786704503</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11442,7 +11346,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>555.555556</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11459,31 +11363,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+          <t>0x91957fcc3f4e1390d64a84f24cad4ac44f2f9926c17ed7cd978de77f93ab840a</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Bundesliga</t>
@@ -11506,7 +11418,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11536,7 +11448,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786682534</t>
+          <t>1786704472</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11546,7 +11458,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>50.328841</t>
+          <t>49.28</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11563,102 +11475,1766 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>0x33ec03964bc9b5353ad6c834080797ae574d6738a2f6ecafd9040ba4d9dc21d6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1786704050</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>49.28</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0x060bae1553ca0b1b27e0303f5cb0b1a208018b22ad43c47887b7eab9174eb11f</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0x1EEc232fcA954D560922A46C0dc77A1d5Fc1278C</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.49999</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.7588</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1786700992</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1.976923</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0x89945f48362d177a1a075c347f0cee9e0d2949251232062e79954c3fdbda8548</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>36.69</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1786697954</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>49.083612</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0x93f8ae4db5435f2088469fb82cd900c151ecf6b1707f1fa749e6f328a01576ca</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>35.77998</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1786696250</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>47.70664</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0x6c37a9cb7783035c2363518b021ca262c492e837d2f5566a7197ec81c9c7de3c</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>557.83</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1786696222</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1025.894253</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0xb8844dc9cad239dda58468ea8057a5d42a49adaeb39f853d1d8a2f72f86b2a27</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>22.83999</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1786695902</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>42.004579</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0x54732df74313495ae4750f10f2ec1b1437622f274d00a56e3a61e0c23a1acde2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>296.6897</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1786695873</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>643.229702</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0x6388d0dbf04f19becbc0ad458a4000da4d11cf0c26aa897bddfdef754fa335a6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>346.54</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>1786695869</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>641.740741</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0x1d90dd2b57deb4a163be22ec0027c40ec930edc46ca3efc1b7765006d5e9eebe</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>1786695799</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1.851852</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0x48c4a72e45740310d60b3a648deeb512824e451ea186d1e82f9627f5d1bccd51</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>1786695700</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1.33332</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0x4ebc4769fdeafa179bcff07b1f83a83c2f713dd0b038325187723d036f03b296</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>484.79999</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>1786695653</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>897.777759</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0xb62e61543153c0b9ab6a1a3fd388b5a709ce3356240d5f06b0b8a0c62bad8b1a</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>1786695037</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0xcb685b4fae14c825bf9607310b4cfb4892294304396aedd620dbe8ca7410b54c</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>1786694953</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0xbd2bb212ebdbf36503fd81ffa846a8c770a6aae66b0380af0fcc4a45aa66cc55</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>LASK Linz -1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>1786694900</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>555.555556</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0x9a4c9495704ee89e4ba79b9b36a31528db556fff6ab2c9dc478536c1cfb4c025</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>23.34</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>LASK Linz vs SV Ried</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>0x01fc28e4c05acb8383b677e0a4bb44b143f7f41bef6d4a5a65902c464ac1e8d9</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>L19722986</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>1786682534</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>1786728600</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>50.328841</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>0xbc3f9a4aae23f8578c48b6575d84b3634a2c81e75a2b7c12b7aa17d431671a0e</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>1.2625</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>LASK Linz vs SV Ried</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>LASK Linz</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>SV Ried</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>0x0f99df90038c8a3c1e5030e6029938911a2c71ab0d65fac4b3536f297fc63cbc</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>L19722986</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
         <is>
           <t>1786678003</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S119" t="inlineStr">
         <is>
           <t>1786728600</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T119" t="inlineStr">
         <is>
           <t>7.92381</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="U119" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
+      <c r="V119" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
